--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179254</v>
+        <v>121178296</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>78598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,34 +1623,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502024</v>
+        <v>502112</v>
       </c>
       <c r="R10" t="n">
-        <v>6981239</v>
+        <v>6981306</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121178296</v>
+        <v>121179254</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>79679</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,34 +1735,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502112</v>
+        <v>502024</v>
       </c>
       <c r="R11" t="n">
-        <v>6981306</v>
+        <v>6981239</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121176899</v>
+        <v>121178413</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>78598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,37 +1847,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501990</v>
+        <v>502129</v>
       </c>
       <c r="R12" t="n">
-        <v>6981209</v>
+        <v>6981301</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121178413</v>
+        <v>121176899</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>79679</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,37 +2071,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502129</v>
+        <v>501990</v>
       </c>
       <c r="R14" t="n">
-        <v>6981301</v>
+        <v>6981209</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121177544</v>
+        <v>121177193</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502019</v>
+        <v>501970</v>
       </c>
       <c r="R2" t="n">
-        <v>6981264</v>
+        <v>6981231</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121178222</v>
+        <v>121179357</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502019</v>
+        <v>501953</v>
       </c>
       <c r="R3" t="n">
-        <v>6981363</v>
+        <v>6981183</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121177193</v>
+        <v>121177666</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501970</v>
+        <v>502036</v>
       </c>
       <c r="R4" t="n">
-        <v>6981231</v>
+        <v>6981290</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -992,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121177666</v>
+        <v>121177544</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,41 +1032,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502036</v>
+        <v>502019</v>
       </c>
       <c r="R5" t="n">
-        <v>6981290</v>
+        <v>6981264</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121179047</v>
+        <v>121177618</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,38 +1153,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502122</v>
+        <v>502046</v>
       </c>
       <c r="R6" t="n">
-        <v>6981282</v>
+        <v>6981269</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121177777</v>
+        <v>121179002</v>
       </c>
       <c r="B7" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,34 +1278,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502028</v>
+        <v>502129</v>
       </c>
       <c r="R7" t="n">
-        <v>6981319</v>
+        <v>6981288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121176974</v>
+        <v>121179233</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,50 +1386,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501987</v>
+        <v>502045</v>
       </c>
       <c r="R8" t="n">
-        <v>6981226</v>
+        <v>6981229</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179435</v>
+        <v>121176651</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501975</v>
+        <v>501993</v>
       </c>
       <c r="R9" t="n">
-        <v>6981149</v>
+        <v>6981209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,7 +1610,7 @@
         <v>121178296</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121179254</v>
+        <v>121177394</v>
       </c>
       <c r="B11" t="n">
-        <v>79679</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,13 +1759,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502024</v>
+        <v>501878</v>
       </c>
       <c r="R11" t="n">
-        <v>6981239</v>
+        <v>6981203</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121178413</v>
+        <v>121178222</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,41 +1843,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502129</v>
+        <v>502019</v>
       </c>
       <c r="R12" t="n">
-        <v>6981301</v>
+        <v>6981363</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121177394</v>
+        <v>121177647</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,41 +1964,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501878</v>
+        <v>502044</v>
       </c>
       <c r="R13" t="n">
-        <v>6981203</v>
+        <v>6981284</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121176899</v>
+        <v>121178413</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,37 +2089,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501990</v>
+        <v>502129</v>
       </c>
       <c r="R14" t="n">
-        <v>6981209</v>
+        <v>6981301</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121177068</v>
+        <v>121179347</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,7 +2220,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2216,13 +2234,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501973</v>
+        <v>501950</v>
       </c>
       <c r="R15" t="n">
-        <v>6981228</v>
+        <v>6981187</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121179068</v>
+        <v>121177777</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,34 +2322,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502095</v>
+        <v>502028</v>
       </c>
       <c r="R16" t="n">
-        <v>6981276</v>
+        <v>6981319</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121179002</v>
+        <v>121179060</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,13 +2458,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502129</v>
+        <v>502105</v>
       </c>
       <c r="R17" t="n">
-        <v>6981288</v>
+        <v>6981279</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2475,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121177618</v>
+        <v>121179047</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,47 +2542,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502046</v>
+        <v>502122</v>
       </c>
       <c r="R18" t="n">
-        <v>6981269</v>
+        <v>6981282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121179357</v>
+        <v>121179323</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2682,13 +2691,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501953</v>
+        <v>501959</v>
       </c>
       <c r="R19" t="n">
-        <v>6981183</v>
+        <v>6981218</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121179347</v>
+        <v>121179068</v>
       </c>
       <c r="B20" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,50 +2775,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501950</v>
+        <v>502095</v>
       </c>
       <c r="R20" t="n">
-        <v>6981187</v>
+        <v>6981276</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121177647</v>
+        <v>121179024</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2887,47 +2887,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502044</v>
+        <v>502138</v>
       </c>
       <c r="R21" t="n">
-        <v>6981284</v>
+        <v>6981282</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2959,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2969,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121179227</v>
+        <v>121178280</v>
       </c>
       <c r="B22" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3012,34 +3003,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502044</v>
+        <v>502085</v>
       </c>
       <c r="R22" t="n">
-        <v>6981240</v>
+        <v>6981304</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3108,10 +3099,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121176651</v>
+        <v>121177622</v>
       </c>
       <c r="B23" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3120,47 +3111,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501993</v>
+        <v>502044</v>
       </c>
       <c r="R23" t="n">
-        <v>6981209</v>
+        <v>6981267</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3202,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3229,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121179060</v>
+        <v>121179435</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3241,41 +3223,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502105</v>
+        <v>501975</v>
       </c>
       <c r="R24" t="n">
-        <v>6981279</v>
+        <v>6981149</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3304,7 +3295,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3314,7 +3305,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121179233</v>
+        <v>121179227</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3357,21 +3348,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,13 +3372,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502045</v>
+        <v>502044</v>
       </c>
       <c r="R25" t="n">
-        <v>6981229</v>
+        <v>6981240</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3416,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3426,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,10 +3444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121179323</v>
+        <v>121179254</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3465,50 +3456,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501959</v>
+        <v>502024</v>
       </c>
       <c r="R26" t="n">
-        <v>6981218</v>
+        <v>6981239</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3537,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121178280</v>
+        <v>121177068</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3586,38 +3568,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502085</v>
+        <v>501973</v>
       </c>
       <c r="R27" t="n">
-        <v>6981304</v>
+        <v>6981228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121177622</v>
+        <v>121176899</v>
       </c>
       <c r="B28" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3702,21 +3693,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3726,13 +3717,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502044</v>
+        <v>501990</v>
       </c>
       <c r="R28" t="n">
-        <v>6981267</v>
+        <v>6981209</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3761,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3798,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121179024</v>
+        <v>121176974</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,41 +3801,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502138</v>
+        <v>501987</v>
       </c>
       <c r="R29" t="n">
-        <v>6981282</v>
+        <v>6981226</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121178413</v>
+        <v>121179347</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,41 +2085,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502129</v>
+        <v>501950</v>
       </c>
       <c r="R14" t="n">
-        <v>6981301</v>
+        <v>6981187</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2148,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121179347</v>
+        <v>121177777</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,50 +2206,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501950</v>
+        <v>502028</v>
       </c>
       <c r="R15" t="n">
-        <v>6981187</v>
+        <v>6981319</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121177777</v>
+        <v>121178413</v>
       </c>
       <c r="B16" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,34 +2322,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502028</v>
+        <v>502129</v>
       </c>
       <c r="R16" t="n">
-        <v>6981319</v>
+        <v>6981301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2530,7 +2530,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121179047</v>
+        <v>121179068</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502122</v>
+        <v>502095</v>
       </c>
       <c r="R18" t="n">
-        <v>6981282</v>
+        <v>6981276</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121179323</v>
+        <v>121179024</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,50 +2654,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501959</v>
+        <v>502138</v>
       </c>
       <c r="R19" t="n">
-        <v>6981218</v>
+        <v>6981282</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2726,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,7 +2754,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121179068</v>
+        <v>121179047</v>
       </c>
       <c r="B20" t="n">
         <v>78601</v>
@@ -2803,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502095</v>
+        <v>502122</v>
       </c>
       <c r="R20" t="n">
-        <v>6981276</v>
+        <v>6981282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2838,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121179024</v>
+        <v>121179323</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2887,41 +2878,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502138</v>
+        <v>501959</v>
       </c>
       <c r="R21" t="n">
-        <v>6981282</v>
+        <v>6981218</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121177193</v>
+        <v>121176899</v>
       </c>
       <c r="B2" t="n">
         <v>79682</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501970</v>
+        <v>501990</v>
       </c>
       <c r="R2" t="n">
-        <v>6981231</v>
+        <v>6981209</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179357</v>
+        <v>121178296</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501953</v>
+        <v>502112</v>
       </c>
       <c r="R3" t="n">
-        <v>6981183</v>
+        <v>6981306</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121177666</v>
+        <v>121178222</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502036</v>
+        <v>502019</v>
       </c>
       <c r="R4" t="n">
-        <v>6981290</v>
+        <v>6981363</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121177544</v>
+        <v>121179435</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502019</v>
+        <v>501975</v>
       </c>
       <c r="R5" t="n">
-        <v>6981264</v>
+        <v>6981149</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121177618</v>
+        <v>121179060</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,50 +1153,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502046</v>
+        <v>502105</v>
       </c>
       <c r="R6" t="n">
-        <v>6981269</v>
+        <v>6981279</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1374,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179233</v>
+        <v>121177544</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,41 +1377,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502045</v>
+        <v>502019</v>
       </c>
       <c r="R8" t="n">
-        <v>6981229</v>
+        <v>6981264</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121176651</v>
+        <v>121178413</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,47 +1498,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501993</v>
+        <v>502129</v>
       </c>
       <c r="R9" t="n">
-        <v>6981209</v>
+        <v>6981301</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121178296</v>
+        <v>121179254</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,34 +1614,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502112</v>
+        <v>502024</v>
       </c>
       <c r="R10" t="n">
-        <v>6981306</v>
+        <v>6981239</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1682,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121177394</v>
+        <v>121176974</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,38 +1722,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501878</v>
+        <v>501987</v>
       </c>
       <c r="R11" t="n">
-        <v>6981203</v>
+        <v>6981226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121178222</v>
+        <v>121179024</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,47 +1843,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502019</v>
+        <v>502138</v>
       </c>
       <c r="R12" t="n">
-        <v>6981363</v>
+        <v>6981282</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1915,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121177647</v>
+        <v>121177193</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,47 +1955,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502044</v>
+        <v>501970</v>
       </c>
       <c r="R13" t="n">
-        <v>6981284</v>
+        <v>6981231</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2036,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121179347</v>
+        <v>121177777</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,50 +2067,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501950</v>
+        <v>502028</v>
       </c>
       <c r="R14" t="n">
-        <v>6981187</v>
+        <v>6981319</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121177777</v>
+        <v>121177618</v>
       </c>
       <c r="B15" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,38 +2179,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502028</v>
+        <v>502046</v>
       </c>
       <c r="R15" t="n">
-        <v>6981319</v>
+        <v>6981269</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121178413</v>
+        <v>121179357</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,41 +2300,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502129</v>
+        <v>501953</v>
       </c>
       <c r="R16" t="n">
-        <v>6981301</v>
+        <v>6981183</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,7 +2409,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121179060</v>
+        <v>121179233</v>
       </c>
       <c r="B17" t="n">
         <v>78601</v>
@@ -2454,14 +2445,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502105</v>
+        <v>502045</v>
       </c>
       <c r="R17" t="n">
-        <v>6981279</v>
+        <v>6981229</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2493,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,7 +2521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121179068</v>
+        <v>121177622</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2566,14 +2557,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502095</v>
+        <v>502044</v>
       </c>
       <c r="R18" t="n">
-        <v>6981276</v>
+        <v>6981267</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121179024</v>
+        <v>121179047</v>
       </c>
       <c r="B19" t="n">
         <v>78601</v>
@@ -2682,13 +2673,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502138</v>
+        <v>502122</v>
       </c>
       <c r="R19" t="n">
         <v>6981282</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121179047</v>
+        <v>121177068</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,38 +2757,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502122</v>
+        <v>501973</v>
       </c>
       <c r="R20" t="n">
-        <v>6981282</v>
+        <v>6981228</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121179323</v>
+        <v>121177666</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,50 +2878,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501959</v>
+        <v>502036</v>
       </c>
       <c r="R21" t="n">
-        <v>6981218</v>
+        <v>6981290</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121178280</v>
+        <v>121179323</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,38 +2990,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502085</v>
+        <v>501959</v>
       </c>
       <c r="R22" t="n">
-        <v>6981304</v>
+        <v>6981218</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,7 +3099,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121177622</v>
+        <v>121179068</v>
       </c>
       <c r="B23" t="n">
         <v>78601</v>
@@ -3135,14 +3135,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502044</v>
+        <v>502095</v>
       </c>
       <c r="R23" t="n">
-        <v>6981267</v>
+        <v>6981276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121179435</v>
+        <v>121179227</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3223,47 +3223,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501975</v>
+        <v>502044</v>
       </c>
       <c r="R24" t="n">
-        <v>6981149</v>
+        <v>6981240</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3295,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3296,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121179227</v>
+        <v>121178280</v>
       </c>
       <c r="B25" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3348,34 +3339,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502044</v>
+        <v>502085</v>
       </c>
       <c r="R25" t="n">
-        <v>6981240</v>
+        <v>6981304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3407,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3444,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121179254</v>
+        <v>121177394</v>
       </c>
       <c r="B26" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3484,13 +3475,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502024</v>
+        <v>501878</v>
       </c>
       <c r="R26" t="n">
-        <v>6981239</v>
+        <v>6981203</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3519,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,7 +3547,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121177068</v>
+        <v>121176651</v>
       </c>
       <c r="B27" t="n">
         <v>98081</v>
@@ -3605,10 +3596,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501973</v>
+        <v>501993</v>
       </c>
       <c r="R27" t="n">
-        <v>6981228</v>
+        <v>6981209</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121176899</v>
+        <v>121179347</v>
       </c>
       <c r="B28" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,38 +3680,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501990</v>
+        <v>501950</v>
       </c>
       <c r="R28" t="n">
-        <v>6981209</v>
+        <v>6981187</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,7 +3789,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121176974</v>
+        <v>121177647</v>
       </c>
       <c r="B29" t="n">
         <v>98081</v>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501987</v>
+        <v>502044</v>
       </c>
       <c r="R29" t="n">
-        <v>6981226</v>
+        <v>6981284</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121178413</v>
+        <v>121179254</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502129</v>
+        <v>502024</v>
       </c>
       <c r="R9" t="n">
-        <v>6981301</v>
+        <v>6981239</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179254</v>
+        <v>121176974</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,41 +1610,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502024</v>
+        <v>501987</v>
       </c>
       <c r="R10" t="n">
-        <v>6981239</v>
+        <v>6981226</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121176974</v>
+        <v>121178413</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,47 +1731,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501987</v>
+        <v>502129</v>
       </c>
       <c r="R11" t="n">
-        <v>6981226</v>
+        <v>6981301</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2288,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121179357</v>
+        <v>121179233</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,47 +2300,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501953</v>
+        <v>502045</v>
       </c>
       <c r="R16" t="n">
-        <v>6981183</v>
+        <v>6981229</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2372,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121179233</v>
+        <v>121177622</v>
       </c>
       <c r="B17" t="n">
         <v>78601</v>
@@ -2449,13 +2440,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502045</v>
+        <v>502044</v>
       </c>
       <c r="R17" t="n">
-        <v>6981229</v>
+        <v>6981267</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121177622</v>
+        <v>121179357</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,41 +2524,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502044</v>
+        <v>501953</v>
       </c>
       <c r="R18" t="n">
-        <v>6981267</v>
+        <v>6981183</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2978,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121179323</v>
+        <v>121179068</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,47 +2990,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501959</v>
+        <v>502095</v>
       </c>
       <c r="R22" t="n">
-        <v>6981218</v>
+        <v>6981276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121179068</v>
+        <v>121179323</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,38 +3102,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502095</v>
+        <v>501959</v>
       </c>
       <c r="R23" t="n">
-        <v>6981276</v>
+        <v>6981218</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121176899</v>
+        <v>121178296</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501990</v>
+        <v>502112</v>
       </c>
       <c r="R2" t="n">
-        <v>6981209</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121178296</v>
+        <v>121179047</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502112</v>
+        <v>502122</v>
       </c>
       <c r="R3" t="n">
-        <v>6981306</v>
+        <v>6981282</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121178222</v>
+        <v>121177622</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,50 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502019</v>
+        <v>502044</v>
       </c>
       <c r="R4" t="n">
-        <v>6981363</v>
+        <v>6981267</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121179435</v>
+        <v>121177777</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501975</v>
+        <v>502028</v>
       </c>
       <c r="R5" t="n">
-        <v>6981149</v>
+        <v>6981319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121179060</v>
+        <v>121177068</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1135,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502105</v>
+        <v>501973</v>
       </c>
       <c r="R6" t="n">
-        <v>6981279</v>
+        <v>6981228</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121179002</v>
+        <v>121179060</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502129</v>
+        <v>502105</v>
       </c>
       <c r="R7" t="n">
-        <v>6981288</v>
+        <v>6981279</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121177544</v>
+        <v>121179233</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,50 +1368,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502019</v>
+        <v>502045</v>
       </c>
       <c r="R8" t="n">
-        <v>6981264</v>
+        <v>6981229</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179254</v>
+        <v>121177618</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,41 +1480,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502024</v>
+        <v>502046</v>
       </c>
       <c r="R9" t="n">
-        <v>6981239</v>
+        <v>6981269</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121176974</v>
+        <v>121178413</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,47 +1601,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501987</v>
+        <v>502129</v>
       </c>
       <c r="R10" t="n">
-        <v>6981226</v>
+        <v>6981301</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121178413</v>
+        <v>121178222</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,41 +1713,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502129</v>
+        <v>502019</v>
       </c>
       <c r="R11" t="n">
-        <v>6981301</v>
+        <v>6981363</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179024</v>
+        <v>121179068</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,13 +1862,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502138</v>
+        <v>502095</v>
       </c>
       <c r="R12" t="n">
-        <v>6981282</v>
+        <v>6981276</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121177193</v>
+        <v>121179002</v>
       </c>
       <c r="B13" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,37 +1950,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501970</v>
+        <v>502129</v>
       </c>
       <c r="R13" t="n">
-        <v>6981231</v>
+        <v>6981288</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121177777</v>
+        <v>121176899</v>
       </c>
       <c r="B14" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,13 +2086,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502028</v>
+        <v>501990</v>
       </c>
       <c r="R14" t="n">
-        <v>6981319</v>
+        <v>6981209</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121177618</v>
+        <v>121177544</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502046</v>
+        <v>502019</v>
       </c>
       <c r="R15" t="n">
-        <v>6981269</v>
+        <v>6981264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2242,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2252,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121179233</v>
+        <v>121179435</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,41 +2291,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502045</v>
+        <v>501975</v>
       </c>
       <c r="R16" t="n">
-        <v>6981229</v>
+        <v>6981149</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121177622</v>
+        <v>121177193</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502044</v>
+        <v>501970</v>
       </c>
       <c r="R17" t="n">
-        <v>6981267</v>
+        <v>6981231</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121179357</v>
+        <v>121179254</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,47 +2524,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501953</v>
+        <v>502024</v>
       </c>
       <c r="R18" t="n">
-        <v>6981183</v>
+        <v>6981239</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2596,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121179047</v>
+        <v>121176974</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,38 +2636,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502122</v>
+        <v>501987</v>
       </c>
       <c r="R19" t="n">
-        <v>6981282</v>
+        <v>6981226</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121177068</v>
+        <v>121179323</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501973</v>
+        <v>501959</v>
       </c>
       <c r="R20" t="n">
-        <v>6981228</v>
+        <v>6981218</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121177666</v>
+        <v>121177394</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502036</v>
+        <v>501878</v>
       </c>
       <c r="R21" t="n">
-        <v>6981290</v>
+        <v>6981203</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121179068</v>
+        <v>121179227</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,34 +2994,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502095</v>
+        <v>502044</v>
       </c>
       <c r="R22" t="n">
-        <v>6981276</v>
+        <v>6981240</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121179323</v>
+        <v>121179347</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501959</v>
+        <v>501950</v>
       </c>
       <c r="R23" t="n">
-        <v>6981218</v>
+        <v>6981187</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121179227</v>
+        <v>121178280</v>
       </c>
       <c r="B24" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,34 +3227,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502044</v>
+        <v>502085</v>
       </c>
       <c r="R24" t="n">
-        <v>6981240</v>
+        <v>6981304</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121178280</v>
+        <v>121177666</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3359,17 +3359,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502085</v>
+        <v>502036</v>
       </c>
       <c r="R25" t="n">
-        <v>6981304</v>
+        <v>6981290</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121177394</v>
+        <v>121177647</v>
       </c>
       <c r="B26" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3447,41 +3447,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501878</v>
+        <v>502044</v>
       </c>
       <c r="R26" t="n">
-        <v>6981203</v>
+        <v>6981284</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3510,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,7 +3559,7 @@
         <v>121176651</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3668,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121179347</v>
+        <v>121179024</v>
       </c>
       <c r="B28" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,47 +3689,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501950</v>
+        <v>502138</v>
       </c>
       <c r="R28" t="n">
-        <v>6981187</v>
+        <v>6981282</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121177647</v>
+        <v>121179357</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502044</v>
+        <v>501953</v>
       </c>
       <c r="R29" t="n">
-        <v>6981284</v>
+        <v>6981183</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121178296</v>
+        <v>121179060</v>
       </c>
       <c r="B2" t="n">
         <v>78604</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502112</v>
+        <v>502105</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981279</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179047</v>
+        <v>121179233</v>
       </c>
       <c r="B3" t="n">
         <v>78604</v>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502122</v>
+        <v>502045</v>
       </c>
       <c r="R3" t="n">
-        <v>6981282</v>
+        <v>6981229</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121177622</v>
+        <v>121177618</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502044</v>
+        <v>502046</v>
       </c>
       <c r="R4" t="n">
-        <v>6981267</v>
+        <v>6981269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121177777</v>
+        <v>121179323</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1032,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502028</v>
+        <v>501959</v>
       </c>
       <c r="R5" t="n">
-        <v>6981319</v>
+        <v>6981218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121177068</v>
+        <v>121177777</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,47 +1153,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501973</v>
+        <v>502028</v>
       </c>
       <c r="R6" t="n">
-        <v>6981228</v>
+        <v>6981319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121179060</v>
+        <v>121177647</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,38 +1265,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502105</v>
+        <v>502044</v>
       </c>
       <c r="R7" t="n">
-        <v>6981279</v>
+        <v>6981284</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1319,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179233</v>
+        <v>121179227</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1390,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,13 +1414,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502045</v>
+        <v>502044</v>
       </c>
       <c r="R8" t="n">
-        <v>6981229</v>
+        <v>6981240</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121177618</v>
+        <v>121179024</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,50 +1498,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502046</v>
+        <v>502138</v>
       </c>
       <c r="R9" t="n">
-        <v>6981269</v>
+        <v>6981282</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,7 +1598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121178413</v>
+        <v>121179002</v>
       </c>
       <c r="B10" t="n">
         <v>78604</v>
@@ -1632,7 +1641,7 @@
         <v>502129</v>
       </c>
       <c r="R10" t="n">
-        <v>6981301</v>
+        <v>6981288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121178222</v>
+        <v>121177544</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,7 +1745,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1753,10 +1762,10 @@
         <v>502019</v>
       </c>
       <c r="R11" t="n">
-        <v>6981363</v>
+        <v>6981264</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179068</v>
+        <v>121179357</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,41 +1843,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502095</v>
+        <v>501953</v>
       </c>
       <c r="R12" t="n">
-        <v>6981276</v>
+        <v>6981183</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179002</v>
+        <v>121179347</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,41 +1964,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502129</v>
+        <v>501950</v>
       </c>
       <c r="R13" t="n">
-        <v>6981288</v>
+        <v>6981187</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121176899</v>
+        <v>121178280</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,37 +2089,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501990</v>
+        <v>502085</v>
       </c>
       <c r="R14" t="n">
-        <v>6981209</v>
+        <v>6981304</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2121,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121177544</v>
+        <v>121178296</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,50 +2197,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502019</v>
+        <v>502112</v>
       </c>
       <c r="R15" t="n">
-        <v>6981264</v>
+        <v>6981306</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2242,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121179435</v>
+        <v>121179047</v>
       </c>
       <c r="B16" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,47 +2309,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501975</v>
+        <v>502122</v>
       </c>
       <c r="R16" t="n">
-        <v>6981149</v>
+        <v>6981282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121177193</v>
+        <v>121177666</v>
       </c>
       <c r="B17" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2425,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501970</v>
+        <v>502036</v>
       </c>
       <c r="R17" t="n">
-        <v>6981231</v>
+        <v>6981290</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2475,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,7 +2521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121179254</v>
+        <v>121177193</v>
       </c>
       <c r="B18" t="n">
         <v>79685</v>
@@ -2552,10 +2561,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502024</v>
+        <v>501970</v>
       </c>
       <c r="R18" t="n">
-        <v>6981239</v>
+        <v>6981231</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2587,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121176974</v>
+        <v>121178222</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,7 +2668,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2673,13 +2682,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501987</v>
+        <v>502019</v>
       </c>
       <c r="R19" t="n">
-        <v>6981226</v>
+        <v>6981363</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2754,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121179323</v>
+        <v>121179068</v>
       </c>
       <c r="B20" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2757,47 +2766,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501959</v>
+        <v>502095</v>
       </c>
       <c r="R20" t="n">
-        <v>6981218</v>
+        <v>6981276</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121177394</v>
+        <v>121176899</v>
       </c>
       <c r="B21" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501878</v>
+        <v>501990</v>
       </c>
       <c r="R21" t="n">
-        <v>6981203</v>
+        <v>6981209</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121179227</v>
+        <v>121178413</v>
       </c>
       <c r="B22" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,34 +2994,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502044</v>
+        <v>502129</v>
       </c>
       <c r="R22" t="n">
-        <v>6981240</v>
+        <v>6981301</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121179347</v>
+        <v>121177622</v>
       </c>
       <c r="B23" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,50 +3102,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501950</v>
+        <v>502044</v>
       </c>
       <c r="R23" t="n">
-        <v>6981187</v>
+        <v>6981267</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,10 +3202,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121178280</v>
+        <v>121176974</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3223,38 +3214,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502085</v>
+        <v>501987</v>
       </c>
       <c r="R24" t="n">
-        <v>6981304</v>
+        <v>6981226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121177666</v>
+        <v>121176651</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,41 +3335,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502036</v>
+        <v>501993</v>
       </c>
       <c r="R25" t="n">
-        <v>6981290</v>
+        <v>6981209</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121177647</v>
+        <v>121179254</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3447,47 +3456,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502044</v>
+        <v>502024</v>
       </c>
       <c r="R26" t="n">
-        <v>6981284</v>
+        <v>6981239</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121176651</v>
+        <v>121177068</v>
       </c>
       <c r="B27" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501993</v>
+        <v>501973</v>
       </c>
       <c r="R27" t="n">
-        <v>6981209</v>
+        <v>6981228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121179024</v>
+        <v>121177394</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3693,37 +3693,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502138</v>
+        <v>501878</v>
       </c>
       <c r="R28" t="n">
-        <v>6981282</v>
+        <v>6981203</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121179357</v>
+        <v>121179435</v>
       </c>
       <c r="B29" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501953</v>
+        <v>501975</v>
       </c>
       <c r="R29" t="n">
-        <v>6981183</v>
+        <v>6981149</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179060</v>
+        <v>121179024</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502105</v>
+        <v>502138</v>
       </c>
       <c r="R2" t="n">
-        <v>6981279</v>
+        <v>6981282</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179233</v>
+        <v>121176974</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502045</v>
+        <v>501987</v>
       </c>
       <c r="R3" t="n">
-        <v>6981229</v>
+        <v>6981226</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121177618</v>
+        <v>121179357</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502046</v>
+        <v>501953</v>
       </c>
       <c r="R4" t="n">
-        <v>6981269</v>
+        <v>6981183</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121179323</v>
+        <v>121179435</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501959</v>
+        <v>501975</v>
       </c>
       <c r="R5" t="n">
-        <v>6981218</v>
+        <v>6981149</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121177777</v>
+        <v>121179002</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,34 +1166,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502028</v>
+        <v>502129</v>
       </c>
       <c r="R6" t="n">
-        <v>6981319</v>
+        <v>6981288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121177647</v>
+        <v>121179227</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,37 +1274,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
@@ -1305,10 +1305,10 @@
         <v>502044</v>
       </c>
       <c r="R7" t="n">
-        <v>6981284</v>
+        <v>6981240</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179227</v>
+        <v>121179047</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,34 +1390,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502044</v>
+        <v>502122</v>
       </c>
       <c r="R8" t="n">
-        <v>6981240</v>
+        <v>6981282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179024</v>
+        <v>121178222</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,38 +1498,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502138</v>
+        <v>502019</v>
       </c>
       <c r="R9" t="n">
-        <v>6981282</v>
+        <v>6981363</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1561,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179002</v>
+        <v>121177666</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,17 +1643,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502129</v>
+        <v>502036</v>
       </c>
       <c r="R10" t="n">
-        <v>6981288</v>
+        <v>6981290</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121177544</v>
+        <v>121176651</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,7 +1754,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1759,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502019</v>
+        <v>501993</v>
       </c>
       <c r="R11" t="n">
-        <v>6981264</v>
+        <v>6981209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179357</v>
+        <v>121177647</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501953</v>
+        <v>502044</v>
       </c>
       <c r="R12" t="n">
-        <v>6981183</v>
+        <v>6981284</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1915,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179347</v>
+        <v>121177618</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,7 +1996,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2001,13 +2010,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501950</v>
+        <v>502046</v>
       </c>
       <c r="R13" t="n">
-        <v>6981187</v>
+        <v>6981269</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,7 +2085,7 @@
         <v>121178280</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2185,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121178296</v>
+        <v>121179068</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,13 +2234,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502112</v>
+        <v>502095</v>
       </c>
       <c r="R15" t="n">
-        <v>6981306</v>
+        <v>6981276</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2260,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121179047</v>
+        <v>121177193</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,37 +2322,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502122</v>
+        <v>501970</v>
       </c>
       <c r="R16" t="n">
-        <v>6981282</v>
+        <v>6981231</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121177666</v>
+        <v>121177777</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,21 +2434,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,13 +2458,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502036</v>
+        <v>502028</v>
       </c>
       <c r="R17" t="n">
-        <v>6981290</v>
+        <v>6981319</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121177193</v>
+        <v>121177394</v>
       </c>
       <c r="B18" t="n">
-        <v>79685</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,21 +2546,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2561,13 +2570,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501970</v>
+        <v>501878</v>
       </c>
       <c r="R18" t="n">
-        <v>6981231</v>
+        <v>6981203</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2596,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121178222</v>
+        <v>121177544</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2668,7 +2677,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2685,10 +2694,10 @@
         <v>502019</v>
       </c>
       <c r="R19" t="n">
-        <v>6981363</v>
+        <v>6981264</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121179068</v>
+        <v>121179060</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,13 +2803,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502095</v>
+        <v>502105</v>
       </c>
       <c r="R20" t="n">
-        <v>6981276</v>
+        <v>6981279</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2829,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121176899</v>
+        <v>121178296</v>
       </c>
       <c r="B21" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,34 +2891,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501990</v>
+        <v>502112</v>
       </c>
       <c r="R21" t="n">
-        <v>6981209</v>
+        <v>6981306</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2941,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121178413</v>
+        <v>121179233</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3014,17 +3023,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502129</v>
+        <v>502045</v>
       </c>
       <c r="R22" t="n">
-        <v>6981301</v>
+        <v>6981229</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3053,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3099,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121177622</v>
+        <v>121179254</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3115,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,13 +3139,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502044</v>
+        <v>502024</v>
       </c>
       <c r="R23" t="n">
-        <v>6981267</v>
+        <v>6981239</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3165,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121176974</v>
+        <v>121177622</v>
       </c>
       <c r="B24" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3214,47 +3223,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501987</v>
+        <v>502044</v>
       </c>
       <c r="R24" t="n">
-        <v>6981226</v>
+        <v>6981267</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121176651</v>
+        <v>121179347</v>
       </c>
       <c r="B25" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>501993</v>
+        <v>501950</v>
       </c>
       <c r="R25" t="n">
-        <v>6981209</v>
+        <v>6981187</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3444,10 +3444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121179254</v>
+        <v>121176899</v>
       </c>
       <c r="B26" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502024</v>
+        <v>501990</v>
       </c>
       <c r="R26" t="n">
-        <v>6981239</v>
+        <v>6981209</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121177068</v>
+        <v>121179323</v>
       </c>
       <c r="B27" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501973</v>
+        <v>501959</v>
       </c>
       <c r="R27" t="n">
-        <v>6981228</v>
+        <v>6981218</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121177394</v>
+        <v>121177068</v>
       </c>
       <c r="B28" t="n">
-        <v>90710</v>
+        <v>98098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,38 +3689,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501878</v>
+        <v>501973</v>
       </c>
       <c r="R28" t="n">
-        <v>6981203</v>
+        <v>6981228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121179435</v>
+        <v>121178413</v>
       </c>
       <c r="B29" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,47 +3810,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501975</v>
+        <v>502129</v>
       </c>
       <c r="R29" t="n">
-        <v>6981149</v>
+        <v>6981301</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179024</v>
+        <v>121179435</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502138</v>
+        <v>501975</v>
       </c>
       <c r="R2" t="n">
-        <v>6981282</v>
+        <v>6981149</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121176974</v>
+        <v>121179002</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501987</v>
+        <v>502129</v>
       </c>
       <c r="R3" t="n">
-        <v>6981226</v>
+        <v>6981288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121179357</v>
+        <v>121178413</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,50 +920,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501953</v>
+        <v>502129</v>
       </c>
       <c r="R4" t="n">
-        <v>6981183</v>
+        <v>6981301</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121179435</v>
+        <v>121177068</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1064,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501975</v>
+        <v>501973</v>
       </c>
       <c r="R5" t="n">
-        <v>6981149</v>
+        <v>6981228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121179002</v>
+        <v>121177666</v>
       </c>
       <c r="B6" t="n">
         <v>78607</v>
@@ -1186,17 +1177,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502129</v>
+        <v>502036</v>
       </c>
       <c r="R6" t="n">
-        <v>6981288</v>
+        <v>6981290</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121179227</v>
+        <v>121177618</v>
       </c>
       <c r="B7" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,38 +1265,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502044</v>
+        <v>502046</v>
       </c>
       <c r="R7" t="n">
-        <v>6981240</v>
+        <v>6981269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179047</v>
+        <v>121176899</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502122</v>
+        <v>501990</v>
       </c>
       <c r="R8" t="n">
-        <v>6981282</v>
+        <v>6981209</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121178222</v>
+        <v>121179227</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,50 +1498,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502019</v>
+        <v>502044</v>
       </c>
       <c r="R9" t="n">
-        <v>6981363</v>
+        <v>6981240</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121177666</v>
+        <v>121177622</v>
       </c>
       <c r="B10" t="n">
         <v>78607</v>
@@ -1647,13 +1638,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502036</v>
+        <v>502044</v>
       </c>
       <c r="R10" t="n">
-        <v>6981290</v>
+        <v>6981267</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121176651</v>
+        <v>121179254</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,50 +1722,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501993</v>
+        <v>502024</v>
       </c>
       <c r="R11" t="n">
-        <v>6981209</v>
+        <v>6981239</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121177647</v>
+        <v>121179233</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,47 +1834,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502044</v>
+        <v>502045</v>
       </c>
       <c r="R12" t="n">
-        <v>6981284</v>
+        <v>6981229</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1924,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121177618</v>
+        <v>121177544</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -2010,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502046</v>
+        <v>502019</v>
       </c>
       <c r="R13" t="n">
-        <v>6981269</v>
+        <v>6981264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121178280</v>
+        <v>121179323</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,38 +2067,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502085</v>
+        <v>501959</v>
       </c>
       <c r="R14" t="n">
-        <v>6981304</v>
+        <v>6981218</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121179068</v>
+        <v>121177777</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,34 +2192,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502095</v>
+        <v>502028</v>
       </c>
       <c r="R15" t="n">
-        <v>6981276</v>
+        <v>6981319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121177193</v>
+        <v>121179047</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,37 +2304,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501970</v>
+        <v>502122</v>
       </c>
       <c r="R16" t="n">
-        <v>6981231</v>
+        <v>6981282</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121177777</v>
+        <v>121179060</v>
       </c>
       <c r="B17" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,37 +2416,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502028</v>
+        <v>502105</v>
       </c>
       <c r="R17" t="n">
-        <v>6981319</v>
+        <v>6981279</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121177394</v>
+        <v>121176651</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,38 +2524,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501878</v>
+        <v>501993</v>
       </c>
       <c r="R18" t="n">
-        <v>6981203</v>
+        <v>6981209</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121177544</v>
+        <v>121178280</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,47 +2645,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502019</v>
+        <v>502085</v>
       </c>
       <c r="R19" t="n">
-        <v>6981264</v>
+        <v>6981304</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121179060</v>
+        <v>121179347</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2775,38 +2757,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502105</v>
+        <v>501950</v>
       </c>
       <c r="R20" t="n">
-        <v>6981279</v>
+        <v>6981187</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2838,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,7 +2866,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121178296</v>
+        <v>121179068</v>
       </c>
       <c r="B21" t="n">
         <v>78607</v>
@@ -2915,13 +2906,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502112</v>
+        <v>502095</v>
       </c>
       <c r="R21" t="n">
-        <v>6981306</v>
+        <v>6981276</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,7 +2978,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121179233</v>
+        <v>121179024</v>
       </c>
       <c r="B22" t="n">
         <v>78607</v>
@@ -3023,14 +3014,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502045</v>
+        <v>502138</v>
       </c>
       <c r="R22" t="n">
-        <v>6981229</v>
+        <v>6981282</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3062,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121179254</v>
+        <v>121178222</v>
       </c>
       <c r="B23" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,38 +3102,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502024</v>
+        <v>502019</v>
       </c>
       <c r="R23" t="n">
-        <v>6981239</v>
+        <v>6981363</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121177622</v>
+        <v>121177394</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502044</v>
+        <v>501878</v>
       </c>
       <c r="R24" t="n">
-        <v>6981267</v>
+        <v>6981203</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121179347</v>
+        <v>121178296</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,47 +3335,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>501950</v>
+        <v>502112</v>
       </c>
       <c r="R25" t="n">
-        <v>6981187</v>
+        <v>6981306</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3407,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3444,7 +3435,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121176899</v>
+        <v>121177193</v>
       </c>
       <c r="B26" t="n">
         <v>79688</v>
@@ -3484,10 +3475,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501990</v>
+        <v>501970</v>
       </c>
       <c r="R26" t="n">
-        <v>6981209</v>
+        <v>6981231</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3519,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,7 +3547,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121179323</v>
+        <v>121177647</v>
       </c>
       <c r="B27" t="n">
         <v>98098</v>
@@ -3605,13 +3596,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501959</v>
+        <v>502044</v>
       </c>
       <c r="R27" t="n">
-        <v>6981218</v>
+        <v>6981284</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,7 +3668,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121177068</v>
+        <v>121176974</v>
       </c>
       <c r="B28" t="n">
         <v>98098</v>
@@ -3712,7 +3703,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3726,10 +3717,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501973</v>
+        <v>501987</v>
       </c>
       <c r="R28" t="n">
-        <v>6981228</v>
+        <v>6981226</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3798,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121178413</v>
+        <v>121179357</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,41 +3801,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502129</v>
+        <v>501953</v>
       </c>
       <c r="R29" t="n">
-        <v>6981301</v>
+        <v>6981183</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179233</v>
+        <v>121177544</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,41 +1834,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502045</v>
+        <v>502019</v>
       </c>
       <c r="R12" t="n">
-        <v>6981229</v>
+        <v>6981264</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121177544</v>
+        <v>121179233</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,50 +1955,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502019</v>
+        <v>502045</v>
       </c>
       <c r="R13" t="n">
-        <v>6981264</v>
+        <v>6981229</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121178296</v>
+        <v>121177647</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,38 +3335,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502112</v>
+        <v>502044</v>
       </c>
       <c r="R25" t="n">
-        <v>6981306</v>
+        <v>6981284</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3398,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121177193</v>
+        <v>121176974</v>
       </c>
       <c r="B26" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3447,41 +3456,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501970</v>
+        <v>501987</v>
       </c>
       <c r="R26" t="n">
-        <v>6981231</v>
+        <v>6981226</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3510,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,7 +3565,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121177647</v>
+        <v>121179357</v>
       </c>
       <c r="B27" t="n">
         <v>98098</v>
@@ -3596,10 +3614,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502044</v>
+        <v>501953</v>
       </c>
       <c r="R27" t="n">
-        <v>6981284</v>
+        <v>6981183</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3631,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3668,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121176974</v>
+        <v>121178296</v>
       </c>
       <c r="B28" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,50 +3698,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501987</v>
+        <v>502112</v>
       </c>
       <c r="R28" t="n">
-        <v>6981226</v>
+        <v>6981306</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121179357</v>
+        <v>121177193</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,47 +3810,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501953</v>
+        <v>501970</v>
       </c>
       <c r="R29" t="n">
-        <v>6981183</v>
+        <v>6981231</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121177647</v>
+        <v>121178296</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,47 +3335,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502044</v>
+        <v>502112</v>
       </c>
       <c r="R25" t="n">
-        <v>6981284</v>
+        <v>6981306</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3407,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3408,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3444,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121176974</v>
+        <v>121177193</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,50 +3447,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501987</v>
+        <v>501970</v>
       </c>
       <c r="R26" t="n">
-        <v>6981226</v>
+        <v>6981231</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3528,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,7 +3547,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121179357</v>
+        <v>121177647</v>
       </c>
       <c r="B27" t="n">
         <v>98098</v>
@@ -3614,10 +3596,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501953</v>
+        <v>502044</v>
       </c>
       <c r="R27" t="n">
-        <v>6981183</v>
+        <v>6981284</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3649,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121178296</v>
+        <v>121176974</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,41 +3680,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502112</v>
+        <v>501987</v>
       </c>
       <c r="R28" t="n">
-        <v>6981306</v>
+        <v>6981226</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3761,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3798,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121177193</v>
+        <v>121179357</v>
       </c>
       <c r="B29" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,38 +3801,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501970</v>
+        <v>501953</v>
       </c>
       <c r="R29" t="n">
-        <v>6981231</v>
+        <v>6981183</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 51421-2024 artfynd.xlsx
+++ b/artfynd/A 51421-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179435</v>
+        <v>121179227</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501975</v>
+        <v>502044</v>
       </c>
       <c r="R2" t="n">
-        <v>6981149</v>
+        <v>6981240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179002</v>
+        <v>121176899</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502129</v>
+        <v>501990</v>
       </c>
       <c r="R3" t="n">
-        <v>6981288</v>
+        <v>6981209</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121178413</v>
+        <v>121179002</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,7 +942,7 @@
         <v>502129</v>
       </c>
       <c r="R4" t="n">
-        <v>6981301</v>
+        <v>6981288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121177068</v>
+        <v>121177666</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501973</v>
+        <v>502036</v>
       </c>
       <c r="R5" t="n">
-        <v>6981228</v>
+        <v>6981290</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121177666</v>
+        <v>121177544</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1135,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502036</v>
+        <v>502019</v>
       </c>
       <c r="R6" t="n">
-        <v>6981290</v>
+        <v>6981264</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121177618</v>
+        <v>121179435</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,7 +1279,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502046</v>
+        <v>501975</v>
       </c>
       <c r="R7" t="n">
-        <v>6981269</v>
+        <v>6981149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121176899</v>
+        <v>121179024</v>
       </c>
       <c r="B8" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,34 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501990</v>
+        <v>502138</v>
       </c>
       <c r="R8" t="n">
-        <v>6981209</v>
+        <v>6981282</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179227</v>
+        <v>121179347</v>
       </c>
       <c r="B9" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,41 +1489,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502044</v>
+        <v>501950</v>
       </c>
       <c r="R9" t="n">
-        <v>6981240</v>
+        <v>6981187</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121177622</v>
+        <v>121176974</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,38 +1610,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502044</v>
+        <v>501987</v>
       </c>
       <c r="R10" t="n">
-        <v>6981267</v>
+        <v>6981226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121179254</v>
+        <v>121177394</v>
       </c>
       <c r="B11" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,13 +1759,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502024</v>
+        <v>501878</v>
       </c>
       <c r="R11" t="n">
-        <v>6981239</v>
+        <v>6981203</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121177544</v>
+        <v>121178296</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,50 +1843,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502019</v>
+        <v>502112</v>
       </c>
       <c r="R12" t="n">
-        <v>6981264</v>
+        <v>6981306</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179233</v>
+        <v>121177618</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,41 +1955,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502045</v>
+        <v>502046</v>
       </c>
       <c r="R13" t="n">
-        <v>6981229</v>
+        <v>6981269</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,7 +2067,7 @@
         <v>121179323</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2176,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121177777</v>
+        <v>121178280</v>
       </c>
       <c r="B15" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,34 +2201,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502028</v>
+        <v>502085</v>
       </c>
       <c r="R15" t="n">
-        <v>6981319</v>
+        <v>6981304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,7 +2300,7 @@
         <v>121179047</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121179060</v>
+        <v>121177647</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,38 +2421,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502105</v>
+        <v>502044</v>
       </c>
       <c r="R17" t="n">
-        <v>6981279</v>
+        <v>6981284</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2475,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121176651</v>
+        <v>121177777</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,47 +2542,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501993</v>
+        <v>502028</v>
       </c>
       <c r="R18" t="n">
-        <v>6981209</v>
+        <v>6981319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121178280</v>
+        <v>121179060</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,13 +2682,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502085</v>
+        <v>502105</v>
       </c>
       <c r="R19" t="n">
-        <v>6981304</v>
+        <v>6981279</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2754,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121179347</v>
+        <v>121179357</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2780,7 +2789,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2794,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501950</v>
+        <v>501953</v>
       </c>
       <c r="R20" t="n">
-        <v>6981187</v>
+        <v>6981183</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2829,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121179068</v>
+        <v>121177193</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,37 +2891,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502095</v>
+        <v>501970</v>
       </c>
       <c r="R21" t="n">
-        <v>6981276</v>
+        <v>6981231</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121179024</v>
+        <v>121178222</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,38 +2999,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502138</v>
+        <v>502019</v>
       </c>
       <c r="R22" t="n">
-        <v>6981282</v>
+        <v>6981363</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3053,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3081,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3108,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121178222</v>
+        <v>121177068</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3125,7 +3143,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3139,13 +3157,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502019</v>
+        <v>501973</v>
       </c>
       <c r="R23" t="n">
-        <v>6981363</v>
+        <v>6981228</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3192,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3202,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,10 +3229,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121177394</v>
+        <v>121179233</v>
       </c>
       <c r="B24" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,21 +3245,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3251,13 +3269,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501878</v>
+        <v>502045</v>
       </c>
       <c r="R24" t="n">
-        <v>6981203</v>
+        <v>6981229</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3286,7 +3304,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,7 +3314,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121178296</v>
+        <v>121179254</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,34 +3357,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
+          <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502112</v>
+        <v>502024</v>
       </c>
       <c r="R25" t="n">
-        <v>6981306</v>
+        <v>6981239</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3398,7 +3416,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,7 +3426,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3453,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121177193</v>
+        <v>121178413</v>
       </c>
       <c r="B26" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,37 +3469,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501970</v>
+        <v>502129</v>
       </c>
       <c r="R26" t="n">
-        <v>6981231</v>
+        <v>6981301</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3510,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121177647</v>
+        <v>121176651</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3582,7 +3600,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3596,13 +3614,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502044</v>
+        <v>501993</v>
       </c>
       <c r="R27" t="n">
-        <v>6981284</v>
+        <v>6981209</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3668,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121176974</v>
+        <v>121179068</v>
       </c>
       <c r="B28" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,47 +3698,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pilgården, Pilgården, Jmt</t>
+          <t>Pilgrimstad, Pilgrimstad, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501987</v>
+        <v>502095</v>
       </c>
       <c r="R28" t="n">
-        <v>6981226</v>
+        <v>6981276</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121179357</v>
+        <v>121177622</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,50 +3810,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pilgården, Pilgården, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501953</v>
+        <v>502044</v>
       </c>
       <c r="R29" t="n">
-        <v>6981183</v>
+        <v>6981267</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
